--- a/자소서/홍석진 취업/채용트래커/Job_Tracker_20260614.xlsx
+++ b/자소서/홍석진 취업/채용트래커/Job_Tracker_20260614.xlsx
@@ -18,13 +18,19 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="000563C1"/>
+      <sz val="9"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="2">
@@ -47,8 +53,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -506,9 +513,9 @@
       <c r="H2" t="n">
         <v>10</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>링크</t>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -554,9 +561,9 @@
       <c r="H3" t="n">
         <v>10</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>링크</t>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -602,9 +609,9 @@
       <c r="H4" t="n">
         <v>6</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>링크</t>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -655,7 +662,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -699,7 +705,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -743,7 +748,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -787,7 +791,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -831,7 +834,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -875,7 +877,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -919,7 +920,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -963,7 +963,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1007,7 +1006,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1051,7 +1049,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1095,7 +1092,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1139,7 +1135,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1183,7 +1178,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1227,7 +1221,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1271,7 +1264,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1315,7 +1307,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1359,7 +1350,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1403,7 +1393,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1447,7 +1436,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1491,7 +1479,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1535,7 +1522,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1579,7 +1565,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1623,7 +1608,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1667,7 +1651,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1711,7 +1694,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1755,7 +1737,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1799,7 +1780,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1843,7 +1823,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1887,7 +1866,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1931,7 +1909,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1975,7 +1952,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2019,7 +1995,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2063,7 +2038,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2107,7 +2081,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2151,7 +2124,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2195,7 +2167,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2239,7 +2210,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2283,7 +2253,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2327,7 +2296,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2371,7 +2339,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2415,7 +2382,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2459,7 +2425,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2503,7 +2468,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2547,7 +2511,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2591,7 +2554,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2635,7 +2597,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2679,7 +2640,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2723,7 +2683,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2767,7 +2726,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2811,7 +2769,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2855,7 +2812,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2899,7 +2855,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2943,7 +2898,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2982,12 +2936,11 @@
       <c r="H58" t="n">
         <v>10</v>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>링크</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
+      <c r="I58" s="1" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3026,12 +2979,11 @@
       <c r="H59" t="n">
         <v>8</v>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>링크</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
+      <c r="I59" s="1" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3070,14 +3022,21 @@
       <c r="H60" t="n">
         <v>8</v>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>링크</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
+      <c r="I60" s="1" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3180,9 +3139,9 @@
       <c r="H2" t="n">
         <v>10</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>링크</t>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -3228,9 +3187,9 @@
       <c r="H3" t="n">
         <v>10</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>링크</t>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -3281,7 +3240,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -3325,7 +3283,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -3369,7 +3326,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -3413,7 +3369,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -3457,7 +3412,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -3501,7 +3455,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -3545,7 +3498,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -3589,7 +3541,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -3633,7 +3584,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -3677,7 +3627,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -3721,7 +3670,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -3765,7 +3713,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -3809,7 +3756,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -3853,7 +3799,6 @@
           <t>링크</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3892,12 +3837,11 @@
       <c r="H18" t="n">
         <v>10</v>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>링크</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
+      <c r="I18" s="1" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3936,12 +3880,11 @@
       <c r="H19" t="n">
         <v>8</v>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>링크</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="I19" s="1" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3980,14 +3923,20 @@
       <c r="H20" t="n">
         <v>8</v>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>링크</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>🔗 지원하기</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>